--- a/docs/bang_tham_so.xlsx
+++ b/docs/bang_tham_so.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="theo_gio" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qua_phan_tan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -897,4 +898,154 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Chi so</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Gia tri</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ghi chu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trung binh khach/ngay (mu)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>702.6</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>14 ngay lam viec tieu chuan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Do lech chuan thuc te (sigma)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Do lech chuan Poisson (sqrt(mu))</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Phuong sai / Trung binh (Var/Mean)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&gt;&gt; 1 cho thay qua phan tan manh</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CV ngay (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CV_ngay^2 sau hieu chinh nhieu Poisson</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(Var(N_d) - mu) / mu^2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CV_ngay sau hieu chinh (%)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>He so nhan ngay dung cho mo phong</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D kiem dinh qua phan tan</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>p-value kiem dinh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.765719831418151e-23</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bác bỏ (mạnh)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>